--- a/Examples/Road River - Composite column - simple.xlsx
+++ b/Examples/Road River - Composite column - simple.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Daven/Projects/Macrostrat/Workbench/Code/macrostrat/submodules/column-ingestion/Examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41072268-D4C1-4C4D-9EEF-D7A7AFC00B50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77101D66-4698-A846-9ECE-B5C2AE1E37FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4360" yWindow="660" windowWidth="25840" windowHeight="21680" tabRatio="747" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4360" yWindow="660" windowWidth="25840" windowHeight="21680" tabRatio="747" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="11" r:id="rId1"/>
@@ -109,9 +109,6 @@
     <t>col_name</t>
   </si>
   <si>
-    <t>col_group</t>
-  </si>
-  <si>
     <t>geom</t>
   </si>
   <si>
@@ -400,9 +397,6 @@
     <t>Road River Group, Cronin Formation</t>
   </si>
   <si>
-    <t>comp_b_pos</t>
-  </si>
-  <si>
     <t>Verbatim Composition</t>
   </si>
   <si>
@@ -521,9 +515,6 @@
   </si>
   <si>
     <t>Boulder rudstone/Megabreccia</t>
-  </si>
-  <si>
-    <t>comp_t_pos</t>
   </si>
   <si>
     <t>2015-2017</t>
@@ -838,7 +829,16 @@
     <t>Strauss_2020</t>
   </si>
   <si>
-    <t>POINT(0,0)</t>
+    <t>LINESTRING(-135.58285 65.884392, -135.614518 65.874512, -135.590261 65.881752, -135.614518 65.874512, -135.63898 65.876358, -135.646407 65.875853, -135.66724 65.873555, -135.666052 65.873173, -135.66813 65.873029, -135.667378 65.873898, -135.669039 65.872632, -135.709033 65.880767, -135.74485 65.877133, -135.745033 65.877033, -135.764983 65.876483, -135.748317 65.876483, -135.759983 65.872133, -135.754891 65.869714, -135.761648 65.867955, -135.763178 65.86773, -135.845633 65.866017)</t>
+  </si>
+  <si>
+    <t>measured</t>
+  </si>
+  <si>
+    <t>section_b_pos</t>
+  </si>
+  <si>
+    <t>section_t_pos</t>
   </si>
 </sst>
 </file>
@@ -848,7 +848,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -865,58 +865,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri (Body)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -981,10 +929,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -996,13 +944,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1018,124 +962,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2 2" xfId="2" xr:uid="{729A2053-F829-0543-9979-05136C2D8C60}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color auto="1"/>
@@ -1516,84 +1368,82 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.5" customWidth="1"/>
-    <col min="2" max="2" width="73.6640625" style="18" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" style="18" customWidth="1"/>
-    <col min="4" max="4" width="24.5" style="16" customWidth="1"/>
+    <col min="2" max="2" width="73.6640625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" style="12" customWidth="1"/>
+    <col min="4" max="4" width="24.5" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Road River Group</t>
-        </is>
+      <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="B2" s="4"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="5"/>
+        <v>27</v>
+      </c>
+      <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="5"/>
+        <v>15</v>
+      </c>
+      <c r="B4" s="4"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="8">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6">
         <f ca="1">TODAY()</f>
         <v>46305</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="B6" s="4"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="B7" s="4"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>249</v>
+        <v>14</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="16">
       <c r="A9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>250</v>
+        <v>30</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1605,49 +1455,49 @@
       <c r="A13" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="5"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="5"/>
+        <v>37</v>
+      </c>
+      <c r="B14" s="4"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="5" t="s">
         <v>29</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+    </row>
+    <row r="17" spans="1:2" ht="16">
+      <c r="A17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14" customHeight="1">
+      <c r="A18" s="3" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" ht="16">
-      <c r="A17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="20" customHeight="1">
+      <c r="B18" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1662,8 +1512,9 @@
   <cols>
     <col min="1" max="1" width="14.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="13.1640625" style="1" customWidth="1"/>
-    <col min="3" max="4" width="15.33203125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="11.33203125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="11.33203125" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="12.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="10.83203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -1680,68 +1531,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="2" customFormat="1" ht="16" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="N1" s="9" t="s">
+      <c r="L1" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="O1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="11" t="s">
+      <c r="R1" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="11" t="s">
+      <c r="S1" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="T1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="T1" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="U1" s="12" t="s">
-        <v>36</v>
+      <c r="U1" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="16" customHeight="1">
@@ -1749,35 +1600,35 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="14">
+        <v>2467.4645029642907</v>
+      </c>
+      <c r="D2" s="14">
+        <v>2472.4</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="26">
+      <c r="F2" s="14">
         <v>290.6645029642907</v>
       </c>
-      <c r="E2" s="26">
+      <c r="G2" s="14">
         <v>295.60000000000008</v>
       </c>
-      <c r="F2" s="26">
-        <v>2467.4645029642907</v>
-      </c>
-      <c r="G2" s="26">
-        <v>2472.4</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="N2"/>
       <c r="O2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="U2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="16" customHeight="1">
@@ -1785,24 +1636,24 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="14">
+        <v>2445.9537239762858</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="26">
+      <c r="F3" s="14">
         <v>269.15372397628573</v>
       </c>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26">
-        <v>2445.9537239762858</v>
-      </c>
-      <c r="G3" s="26"/>
+      <c r="G3" s="14"/>
       <c r="H3" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="16" customHeight="1">
@@ -1810,21 +1661,21 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="14">
+        <v>2440.7533158692959</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="26">
+      <c r="F4" s="14">
         <v>263.95331586929552</v>
       </c>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26">
-        <v>2440.7533158692959</v>
-      </c>
-      <c r="G4" s="26"/>
+      <c r="G4" s="14"/>
       <c r="P4" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="16" customHeight="1">
@@ -1832,25 +1683,25 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="14">
+        <v>2434.5992279056945</v>
+      </c>
+      <c r="D5" s="14">
+        <v>2438.2386984695991</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="26">
+      <c r="F5" s="14">
         <v>257.79922790569424</v>
       </c>
-      <c r="E5" s="26">
+      <c r="G5" s="14">
         <v>261.43869846959882</v>
       </c>
-      <c r="F5" s="26">
-        <v>2434.5992279056945</v>
-      </c>
-      <c r="G5" s="26">
-        <v>2438.2386984695991</v>
-      </c>
       <c r="P5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="16" customHeight="1">
@@ -1858,24 +1709,24 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="14">
+        <v>2369.3536688266927</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="26">
+      <c r="F6" s="14">
         <v>192.55366882669242</v>
       </c>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26">
-        <v>2369.3536688266927</v>
-      </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="14"/>
       <c r="L6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="16" customHeight="1">
@@ -1883,21 +1734,21 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="14">
+        <v>2335.4165228181446</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="F7" s="14">
         <v>158.61652281814423</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26">
-        <v>2335.4165228181446</v>
-      </c>
-      <c r="G7" s="26"/>
+      <c r="G7" s="14"/>
       <c r="P7" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="16" customHeight="1">
@@ -1905,27 +1756,27 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="14">
+        <v>2323.7848890114437</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="F8" s="14">
         <v>146.98488901144356</v>
       </c>
-      <c r="E8" s="26"/>
-      <c r="F8" s="26">
-        <v>2323.7848890114437</v>
-      </c>
-      <c r="G8" s="26"/>
-      <c r="L8" s="31" t="s">
-        <v>185</v>
+      <c r="G8" s="14"/>
+      <c r="L8" s="19" t="s">
+        <v>182</v>
       </c>
       <c r="M8" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="16" customHeight="1">
@@ -1933,25 +1784,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2279.1331090583208</v>
+      </c>
+      <c r="D9" s="14">
+        <v>2318.4173831517996</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="26">
+      <c r="F9" s="14">
         <v>102.3331090583207</v>
       </c>
-      <c r="E9" s="26">
+      <c r="G9" s="14">
         <v>141.61738315179926</v>
       </c>
-      <c r="F9" s="26">
-        <v>2279.1331090583208</v>
-      </c>
-      <c r="G9" s="26">
-        <v>2318.4173831517996</v>
-      </c>
       <c r="P9" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="16" customHeight="1">
@@ -1959,21 +1810,21 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="14">
+        <v>2266.3073376533848</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="F10" s="14">
+        <v>89.507337653384809</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="P10" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D10" s="26">
-        <v>89.507337653384809</v>
-      </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26">
-        <v>2266.3073376533848</v>
-      </c>
-      <c r="G10" s="26"/>
-      <c r="P10" s="1" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="16" customHeight="1">
@@ -1981,21 +1832,21 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="14">
+        <v>2240.5213015304016</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="F11" s="14">
         <v>63.721301530401213</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26">
-        <v>2240.5213015304016</v>
-      </c>
-      <c r="G11" s="26"/>
+      <c r="G11" s="14"/>
       <c r="P11" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="16" customHeight="1">
@@ -2003,21 +1854,21 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="14">
+        <v>2232.8674093478562</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="26">
+      <c r="F12" s="14">
         <v>56.067409347856056</v>
       </c>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26">
-        <v>2232.8674093478562</v>
-      </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="14"/>
       <c r="P12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="16" customHeight="1">
@@ -2025,21 +1876,21 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2217.7063449607062</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="26">
+      <c r="F13" s="14">
         <v>40.906344960705916</v>
       </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26">
-        <v>2217.7063449607062</v>
-      </c>
-      <c r="G13" s="26"/>
+      <c r="G13" s="14"/>
       <c r="P13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="16" customHeight="1">
@@ -2047,28 +1898,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="14">
+        <v>2187.9466427685097</v>
+      </c>
+      <c r="D14" s="14">
+        <v>2214.2706521439404</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="26">
+      <c r="F14" s="14">
         <v>11.146642768509583</v>
       </c>
-      <c r="E14" s="26">
+      <c r="G14" s="14">
         <v>37.470652143940441</v>
       </c>
-      <c r="F14" s="26">
-        <v>2187.9466427685097</v>
-      </c>
-      <c r="G14" s="26">
-        <v>2214.2706521439404</v>
-      </c>
       <c r="L14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="16" customHeight="1">
@@ -2076,30 +1927,30 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="14">
+        <v>2176.8000000000002</v>
+      </c>
+      <c r="D15" s="14"/>
+      <c r="E15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="26">
+      <c r="F15" s="14">
         <v>0</v>
       </c>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26">
-        <v>2176.8000000000002</v>
-      </c>
-      <c r="G15" s="26"/>
+      <c r="G15" s="14"/>
       <c r="H15" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="16" customHeight="1">
@@ -2107,29 +1958,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D16" s="26">
+        <v>63</v>
+      </c>
+      <c r="C16" s="14">
+        <v>2173.1857098322839</v>
+      </c>
+      <c r="D16" s="14"/>
+      <c r="E16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" s="14">
         <v>89.285709832283828</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>92.90000000000002</v>
       </c>
-      <c r="F16" s="26">
-        <v>2173.1857098322839</v>
-      </c>
-      <c r="G16" s="26"/>
       <c r="J16" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="M16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:19" ht="16" customHeight="1">
@@ -2137,21 +1988,21 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D17" s="26">
+        <v>63</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2168.1465552715258</v>
+      </c>
+      <c r="D17" s="14"/>
+      <c r="E17" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="14">
         <v>84.246555271525679</v>
       </c>
-      <c r="E17" s="26"/>
-      <c r="F17" s="26">
-        <v>2168.1465552715258</v>
-      </c>
-      <c r="G17" s="26"/>
+      <c r="G17" s="14"/>
       <c r="P17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="16" customHeight="1">
@@ -2159,21 +2010,21 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D18" s="26">
+        <v>63</v>
+      </c>
+      <c r="C18" s="14">
+        <v>2166.8578059729412</v>
+      </c>
+      <c r="D18" s="14"/>
+      <c r="E18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F18" s="14">
         <v>82.957805972940974</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26">
-        <v>2166.8578059729412</v>
-      </c>
-      <c r="G18" s="26"/>
+      <c r="G18" s="14"/>
       <c r="P18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:19" ht="16" customHeight="1">
@@ -2181,21 +2032,21 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D19" s="26">
+        <v>63</v>
+      </c>
+      <c r="C19" s="14">
+        <v>2159.7450682710892</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F19" s="14">
         <v>75.845068271089232</v>
       </c>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26">
-        <v>2159.7450682710892</v>
-      </c>
-      <c r="G19" s="26"/>
+      <c r="G19" s="14"/>
       <c r="P19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="16" customHeight="1">
@@ -2203,30 +2054,30 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D20" s="26">
+        <v>63</v>
+      </c>
+      <c r="C20" s="14">
+        <v>2136.8748363364302</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="14">
         <v>52.974836336429959</v>
       </c>
-      <c r="E20" s="26"/>
-      <c r="F20" s="26">
-        <v>2136.8748363364302</v>
-      </c>
-      <c r="G20" s="26"/>
+      <c r="G20" s="14"/>
       <c r="H20" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L20" s="31" t="s">
-        <v>187</v>
+        <v>164</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>184</v>
       </c>
       <c r="M20" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="16" customHeight="1">
@@ -2234,28 +2085,28 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" s="26">
+        <v>63</v>
+      </c>
+      <c r="C21" s="14">
+        <v>2116.5154934846314</v>
+      </c>
+      <c r="D21" s="14">
+        <v>2133.127327140096</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="14">
         <v>32.615493484631216</v>
       </c>
-      <c r="E21" s="26">
+      <c r="G21" s="14">
         <v>49.227327140096023</v>
       </c>
-      <c r="F21" s="26">
-        <v>2116.5154934846314</v>
-      </c>
-      <c r="G21" s="26">
-        <v>2133.127327140096</v>
-      </c>
       <c r="L21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="16" customHeight="1">
@@ -2263,21 +2114,21 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" s="26">
+        <v>63</v>
+      </c>
+      <c r="C22" s="14">
+        <v>2100.0542552528213</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="14">
         <v>16.154255252821251</v>
       </c>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26">
-        <v>2100.0542552528213</v>
-      </c>
-      <c r="G22" s="26"/>
+      <c r="G22" s="14"/>
       <c r="P22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="16" customHeight="1">
@@ -2285,21 +2136,21 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="26">
+        <v>63</v>
+      </c>
+      <c r="C23" s="14">
+        <v>2095.8520637196834</v>
+      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="14">
         <v>11.952063719683274</v>
       </c>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26">
-        <v>2095.8520637196834</v>
-      </c>
-      <c r="G23" s="26"/>
+      <c r="G23" s="14"/>
       <c r="P23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="16" customHeight="1">
@@ -2307,21 +2158,21 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D24" s="26">
+        <v>63</v>
+      </c>
+      <c r="C24" s="14">
+        <v>2092.9009726292165</v>
+      </c>
+      <c r="D24" s="14"/>
+      <c r="E24" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="14">
         <v>9.000972629216287</v>
       </c>
-      <c r="E24" s="26"/>
-      <c r="F24" s="26">
-        <v>2092.9009726292165</v>
-      </c>
-      <c r="G24" s="26"/>
+      <c r="G24" s="14"/>
       <c r="P24" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="16" customHeight="1">
@@ -2329,21 +2180,21 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D25" s="26">
+        <v>63</v>
+      </c>
+      <c r="C25" s="14">
+        <v>2088.5916266600161</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F25" s="14">
         <v>4.6916266600162109</v>
       </c>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26">
-        <v>2088.5916266600161</v>
-      </c>
-      <c r="G25" s="26"/>
+      <c r="G25" s="14"/>
       <c r="P25" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:19" ht="16" customHeight="1">
@@ -2351,30 +2202,30 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="26">
+        <v>63</v>
+      </c>
+      <c r="C26" s="14">
+        <v>2083.9</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="14">
         <v>0</v>
       </c>
-      <c r="E26" s="26"/>
-      <c r="F26" s="26">
-        <v>2083.9</v>
-      </c>
-      <c r="G26" s="26"/>
+      <c r="G26" s="14"/>
       <c r="H26" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:19" ht="16" customHeight="1">
@@ -2382,29 +2233,29 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" s="26">
+        <v>63</v>
+      </c>
+      <c r="C27" s="14">
+        <v>2077.6528574738386</v>
+      </c>
+      <c r="D27" s="14"/>
+      <c r="E27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="14">
         <v>190.28583426651733</v>
       </c>
-      <c r="E27" s="26">
+      <c r="G27" s="14">
         <v>196.53297679267865</v>
       </c>
-      <c r="F27" s="26">
-        <v>2077.6528574738386</v>
-      </c>
-      <c r="G27" s="26"/>
       <c r="J27" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28" spans="1:19" ht="16" customHeight="1">
@@ -2412,36 +2263,36 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28" s="26">
+        <v>63</v>
+      </c>
+      <c r="C28" s="14">
+        <v>2060.8026817778123</v>
+      </c>
+      <c r="D28" s="14"/>
+      <c r="E28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F28" s="14">
         <v>173.43565857049077</v>
       </c>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26">
-        <v>2060.8026817778123</v>
-      </c>
-      <c r="G28" s="26"/>
+      <c r="G28" s="14"/>
       <c r="H28" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="S28" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="16" customHeight="1">
@@ -2449,30 +2300,30 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="26">
+        <v>63</v>
+      </c>
+      <c r="C29" s="14">
+        <v>2051.3001814882032</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F29" s="14">
         <v>163.93315828088197</v>
       </c>
-      <c r="E29" s="26"/>
-      <c r="F29" s="26">
-        <v>2051.3001814882032</v>
-      </c>
-      <c r="G29" s="26"/>
+      <c r="G29" s="14"/>
       <c r="J29" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="K29">
         <v>1</v>
       </c>
       <c r="M29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="16" customHeight="1">
@@ -2480,21 +2331,21 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C30" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C30" s="14">
+        <v>2009.7573773023903</v>
+      </c>
+      <c r="D30" s="14"/>
+      <c r="E30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F30" s="14">
+        <v>122.39035409506893</v>
+      </c>
+      <c r="G30" s="14"/>
+      <c r="P30" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D30" s="26">
-        <v>122.39035409506893</v>
-      </c>
-      <c r="E30" s="26"/>
-      <c r="F30" s="26">
-        <v>2009.7573773023903</v>
-      </c>
-      <c r="G30" s="26"/>
-      <c r="P30" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:19" ht="16" customHeight="1">
@@ -2502,21 +2353,21 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="26">
+        <v>63</v>
+      </c>
+      <c r="C31" s="14">
+        <v>1974.7576572575974</v>
+      </c>
+      <c r="D31" s="14"/>
+      <c r="E31" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F31" s="14">
         <v>87.390634050276091</v>
       </c>
-      <c r="E31" s="26"/>
-      <c r="F31" s="26">
-        <v>1974.7576572575974</v>
-      </c>
-      <c r="G31" s="26"/>
+      <c r="G31" s="14"/>
       <c r="P31" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="32" spans="1:19" ht="16" customHeight="1">
@@ -2524,21 +2375,21 @@
         <v>31</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32" s="26">
+        <v>63</v>
+      </c>
+      <c r="C32" s="14">
+        <v>1970.9936498436114</v>
+      </c>
+      <c r="D32" s="14"/>
+      <c r="E32" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F32" s="14">
         <v>83.626626636289913</v>
       </c>
-      <c r="E32" s="26"/>
-      <c r="F32" s="26">
-        <v>1970.9936498436114</v>
-      </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="14"/>
       <c r="P32" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1">
@@ -2546,24 +2397,24 @@
         <v>32</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="26">
+        <v>63</v>
+      </c>
+      <c r="C33" s="14">
+        <v>1959.9004633741361</v>
+      </c>
+      <c r="D33" s="14"/>
+      <c r="E33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F33" s="14">
         <v>72.533440166814685</v>
       </c>
-      <c r="E33" s="26"/>
-      <c r="F33" s="26">
-        <v>1959.9004633741361</v>
-      </c>
-      <c r="G33" s="26"/>
+      <c r="G33" s="14"/>
       <c r="M33" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1">
@@ -2571,21 +2422,21 @@
         <v>33</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="26">
+        <v>63</v>
+      </c>
+      <c r="C34" s="14">
+        <v>1950.5320616287602</v>
+      </c>
+      <c r="D34" s="14"/>
+      <c r="E34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" s="14">
         <v>63.16503842143878</v>
       </c>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26">
-        <v>1950.5320616287602</v>
-      </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="14"/>
       <c r="P34" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="16" customHeight="1">
@@ -2593,21 +2444,21 @@
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="26">
+        <v>63</v>
+      </c>
+      <c r="C35" s="14">
+        <v>1948.9506236243581</v>
+      </c>
+      <c r="D35" s="14"/>
+      <c r="E35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="14">
         <v>61.58360041703672</v>
       </c>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26">
-        <v>1948.9506236243581</v>
-      </c>
-      <c r="G35" s="26"/>
+      <c r="G35" s="14"/>
       <c r="P35" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="16" customHeight="1">
@@ -2615,21 +2466,21 @@
         <v>35</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="26">
+        <v>63</v>
+      </c>
+      <c r="C36" s="14">
+        <v>1915.9392613043983</v>
+      </c>
+      <c r="D36" s="14"/>
+      <c r="E36" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F36" s="14">
         <v>28.572238097076877</v>
       </c>
-      <c r="E36" s="26"/>
-      <c r="F36" s="26">
-        <v>1915.9392613043983</v>
-      </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="14"/>
       <c r="P36" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="37" spans="1:19" ht="16" customHeight="1">
@@ -2637,21 +2488,21 @@
         <v>36</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37" s="26">
+        <v>63</v>
+      </c>
+      <c r="C37" s="14">
+        <v>1904.2958083947949</v>
+      </c>
+      <c r="D37" s="14"/>
+      <c r="E37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="14">
         <v>16.928785187473451</v>
       </c>
-      <c r="E37" s="26"/>
-      <c r="F37" s="26">
-        <v>1904.2958083947949</v>
-      </c>
-      <c r="G37" s="26"/>
+      <c r="G37" s="14"/>
       <c r="P37" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:19" ht="16" customHeight="1">
@@ -2659,24 +2510,24 @@
         <v>37</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38" s="26">
+        <v>63</v>
+      </c>
+      <c r="C38" s="14">
+        <v>1894.0673263312353</v>
+      </c>
+      <c r="D38" s="14"/>
+      <c r="E38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F38" s="14">
         <v>6.7003031239139688</v>
       </c>
-      <c r="E38" s="26"/>
-      <c r="F38" s="26">
-        <v>1894.0673263312353</v>
-      </c>
-      <c r="G38" s="26"/>
+      <c r="G38" s="14"/>
       <c r="L38" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="16" customHeight="1">
@@ -2684,49 +2535,49 @@
         <v>38</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="26">
+        <v>63</v>
+      </c>
+      <c r="C39" s="14">
+        <v>1887.3670232073214</v>
+      </c>
+      <c r="D39" s="14"/>
+      <c r="E39" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F39" s="14">
         <v>0</v>
       </c>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26">
-        <v>1887.3670232073214</v>
-      </c>
-      <c r="G39" s="26"/>
+      <c r="G39" s="14"/>
       <c r="H39" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="L39" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="16" customHeight="1">
       <c r="B40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D40" s="26">
+        <v>63</v>
+      </c>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F40" s="14">
         <v>35.189307641811787</v>
       </c>
-      <c r="E40" s="26">
+      <c r="G40" s="14">
         <v>43</v>
       </c>
-      <c r="F40" s="26"/>
-      <c r="G40" s="26"/>
       <c r="H40" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="41" spans="1:19" ht="16" customHeight="1">
@@ -2734,28 +2585,28 @@
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="26">
+        <v>63</v>
+      </c>
+      <c r="C41" s="14">
+        <v>1867.8348766266363</v>
+      </c>
+      <c r="D41" s="14">
+        <v>1879.589307641812</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F41" s="14">
         <v>23.434876626636285</v>
       </c>
-      <c r="E41" s="26">
+      <c r="G41" s="14">
         <v>35.189307641811787</v>
       </c>
-      <c r="F41" s="26">
-        <v>1867.8348766266363</v>
-      </c>
-      <c r="G41" s="26">
-        <v>1879.589307641812</v>
-      </c>
       <c r="L41" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:19" ht="16" customHeight="1">
@@ -2763,24 +2614,24 @@
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D42" s="26">
+        <v>63</v>
+      </c>
+      <c r="C42" s="14">
+        <v>1863.3310151755031</v>
+      </c>
+      <c r="D42" s="14"/>
+      <c r="E42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F42" s="14">
         <v>18.931015175502949</v>
       </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26">
-        <v>1863.3310151755031</v>
-      </c>
-      <c r="G42" s="26"/>
+      <c r="G42" s="14"/>
       <c r="H42" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:19" ht="16" customHeight="1">
@@ -2788,24 +2639,24 @@
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D43" s="26">
+        <v>63</v>
+      </c>
+      <c r="C43" s="14">
+        <v>1859.1184712514964</v>
+      </c>
+      <c r="D43" s="14"/>
+      <c r="E43" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F43" s="14">
         <v>14.718471251496309</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="26">
-        <v>1859.1184712514964</v>
-      </c>
-      <c r="G43" s="26"/>
+      <c r="G43" s="14"/>
       <c r="J43" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="16" customHeight="1">
@@ -2813,33 +2664,33 @@
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D44" s="26">
+        <v>63</v>
+      </c>
+      <c r="C44" s="14">
+        <v>1844.4</v>
+      </c>
+      <c r="D44" s="14"/>
+      <c r="E44" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F44" s="14">
         <v>0</v>
       </c>
-      <c r="E44" s="26"/>
-      <c r="F44" s="26">
-        <v>1844.4</v>
-      </c>
-      <c r="G44" s="26"/>
+      <c r="G44" s="14"/>
       <c r="H44" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S44" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="45" spans="1:19" ht="16" customHeight="1">
@@ -2847,35 +2698,35 @@
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D45" s="26">
+        <v>63</v>
+      </c>
+      <c r="C45" s="14">
+        <v>1830.7866743884231</v>
+      </c>
+      <c r="D45" s="14"/>
+      <c r="E45" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F45" s="14">
         <v>275.08667438842298</v>
       </c>
-      <c r="E45" s="26">
+      <c r="G45" s="14">
         <v>288.70000000000005</v>
       </c>
-      <c r="F45" s="26">
-        <v>1830.7866743884231</v>
-      </c>
-      <c r="G45" s="26"/>
       <c r="H45" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I45" s="1">
         <v>0.99</v>
       </c>
       <c r="J45" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L45" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:19" ht="16" customHeight="1">
@@ -2883,31 +2734,31 @@
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D46" s="26">
+        <v>63</v>
+      </c>
+      <c r="C46" s="14">
+        <v>1821.9998548681951</v>
+      </c>
+      <c r="D46" s="14">
+        <v>1828.5708326937302</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F46" s="14">
         <v>266.29985486819521</v>
       </c>
-      <c r="E46" s="26">
+      <c r="G46" s="14">
         <v>272.87083269373005</v>
       </c>
-      <c r="F46" s="26">
-        <v>1821.9998548681951</v>
-      </c>
-      <c r="G46" s="26">
-        <v>1828.5708326937302</v>
-      </c>
       <c r="L46" t="s">
-        <v>193</v>
-      </c>
-      <c r="M46" s="31" t="s">
-        <v>193</v>
+        <v>190</v>
+      </c>
+      <c r="M46" s="19" t="s">
+        <v>190</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47" spans="1:19" ht="16" customHeight="1">
@@ -2915,21 +2766,21 @@
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D47" s="26">
+        <v>63</v>
+      </c>
+      <c r="C47" s="14">
+        <v>1801.513391199989</v>
+      </c>
+      <c r="D47" s="14"/>
+      <c r="E47" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F47" s="14">
         <v>245.81339119998884</v>
       </c>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26">
-        <v>1801.513391199989</v>
-      </c>
-      <c r="G47" s="26"/>
+      <c r="G47" s="14"/>
       <c r="P47" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="48" spans="1:19" ht="16" customHeight="1">
@@ -2937,21 +2788,21 @@
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D48" s="26">
+        <v>63</v>
+      </c>
+      <c r="C48" s="14">
+        <v>1798.5320769198565</v>
+      </c>
+      <c r="D48" s="14"/>
+      <c r="E48" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F48" s="14">
         <v>242.83207691985655</v>
       </c>
-      <c r="E48" s="26"/>
-      <c r="F48" s="26">
-        <v>1798.5320769198565</v>
-      </c>
-      <c r="G48" s="26"/>
+      <c r="G48" s="14"/>
       <c r="P48" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="16" customHeight="1">
@@ -2959,21 +2810,21 @@
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D49" s="26">
+        <v>63</v>
+      </c>
+      <c r="C49" s="14">
+        <v>1791.2721737674262</v>
+      </c>
+      <c r="D49" s="14"/>
+      <c r="E49" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F49" s="14">
         <v>235.57217376742628</v>
       </c>
-      <c r="E49" s="26"/>
-      <c r="F49" s="26">
-        <v>1791.2721737674262</v>
-      </c>
-      <c r="G49" s="26"/>
+      <c r="G49" s="14"/>
       <c r="P49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="16" customHeight="1">
@@ -2981,27 +2832,27 @@
         <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" s="26">
+        <v>63</v>
+      </c>
+      <c r="C50" s="14">
+        <v>1786.6833670578712</v>
+      </c>
+      <c r="D50" s="14"/>
+      <c r="E50" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="14">
         <v>230.98336705787131</v>
       </c>
-      <c r="E50" s="26"/>
-      <c r="F50" s="26">
-        <v>1786.6833670578712</v>
-      </c>
-      <c r="G50" s="26"/>
-      <c r="L50" s="31" t="s">
-        <v>195</v>
+      <c r="G50" s="14"/>
+      <c r="L50" s="19" t="s">
+        <v>192</v>
       </c>
       <c r="M50" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:16" ht="16" customHeight="1">
@@ -3009,24 +2860,24 @@
         <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D51" s="26">
+        <v>63</v>
+      </c>
+      <c r="C51" s="14">
+        <v>1776.135960591133</v>
+      </c>
+      <c r="D51" s="14"/>
+      <c r="E51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" s="14">
         <v>220.43596059113301</v>
       </c>
-      <c r="E51" s="26"/>
-      <c r="F51" s="26">
-        <v>1776.135960591133</v>
-      </c>
-      <c r="G51" s="26"/>
+      <c r="G51" s="14"/>
       <c r="L51" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:16" ht="16" customHeight="1">
@@ -3034,21 +2885,21 @@
         <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D52" s="26">
+        <v>63</v>
+      </c>
+      <c r="C52" s="14">
+        <v>1775.1166734115743</v>
+      </c>
+      <c r="D52" s="14"/>
+      <c r="E52" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F52" s="14">
         <v>219.41667341157427</v>
       </c>
-      <c r="E52" s="26"/>
-      <c r="F52" s="26">
-        <v>1775.1166734115743</v>
-      </c>
-      <c r="G52" s="26"/>
+      <c r="G52" s="14"/>
       <c r="P52" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="16" customHeight="1">
@@ -3056,27 +2907,27 @@
         <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D53" s="26">
+        <v>63</v>
+      </c>
+      <c r="C53" s="14">
+        <v>1749.980970987594</v>
+      </c>
+      <c r="D53" s="14"/>
+      <c r="E53" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F53" s="14">
         <v>194.28097098759403</v>
       </c>
-      <c r="E53" s="26"/>
-      <c r="F53" s="26">
-        <v>1749.980970987594</v>
-      </c>
-      <c r="G53" s="26"/>
-      <c r="L53" s="31" t="s">
-        <v>196</v>
+      <c r="G53" s="14"/>
+      <c r="L53" s="19" t="s">
+        <v>193</v>
       </c>
       <c r="M53" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="16" customHeight="1">
@@ -3084,21 +2935,21 @@
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D54" s="26">
+        <v>63</v>
+      </c>
+      <c r="C54" s="14">
+        <v>1746.4557682914917</v>
+      </c>
+      <c r="D54" s="14"/>
+      <c r="E54" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F54" s="14">
         <v>190.75576829149165</v>
       </c>
-      <c r="E54" s="26"/>
-      <c r="F54" s="26">
-        <v>1746.4557682914917</v>
-      </c>
-      <c r="G54" s="26"/>
+      <c r="G54" s="14"/>
       <c r="P54" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="16" customHeight="1">
@@ -3106,27 +2957,27 @@
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D55" s="26">
+        <v>63</v>
+      </c>
+      <c r="C55" s="14">
+        <v>1734.7319513250254</v>
+      </c>
+      <c r="D55" s="14"/>
+      <c r="E55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="14">
         <v>179.03195132502546</v>
       </c>
-      <c r="E55" s="26"/>
-      <c r="F55" s="26">
-        <v>1734.7319513250254</v>
-      </c>
-      <c r="G55" s="26"/>
-      <c r="L55" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="M55" s="31" t="s">
-        <v>197</v>
+      <c r="G55" s="14"/>
+      <c r="L55" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="M55" s="19" t="s">
+        <v>194</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="16" customHeight="1">
@@ -3134,21 +2985,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C56" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D56" s="26">
+        <v>63</v>
+      </c>
+      <c r="C56" s="14">
+        <v>1733.7126641454668</v>
+      </c>
+      <c r="D56" s="14"/>
+      <c r="E56" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="14">
         <v>178.01266414546672</v>
       </c>
-      <c r="E56" s="26"/>
-      <c r="F56" s="26">
-        <v>1733.7126641454668</v>
-      </c>
-      <c r="G56" s="26"/>
+      <c r="G56" s="14"/>
       <c r="P56" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57" spans="1:16" ht="16" customHeight="1">
@@ -3156,24 +3007,24 @@
         <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="26">
+        <v>63</v>
+      </c>
+      <c r="C57" s="14">
+        <v>1728.6001130353479</v>
+      </c>
+      <c r="D57" s="14"/>
+      <c r="E57" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F57" s="14">
         <v>172.90011303534797</v>
       </c>
-      <c r="E57" s="26"/>
-      <c r="F57" s="26">
-        <v>1728.6001130353479</v>
-      </c>
-      <c r="G57" s="26"/>
+      <c r="G57" s="14"/>
       <c r="M57" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="16" customHeight="1">
@@ -3181,21 +3032,21 @@
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D58" s="26">
+        <v>63</v>
+      </c>
+      <c r="C58" s="14">
+        <v>1727.5848546588704</v>
+      </c>
+      <c r="D58" s="14"/>
+      <c r="E58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F58" s="14">
         <v>171.88485465887049</v>
       </c>
-      <c r="E58" s="26"/>
-      <c r="F58" s="26">
-        <v>1727.5848546588704</v>
-      </c>
-      <c r="G58" s="26"/>
+      <c r="G58" s="14"/>
       <c r="P58" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="16" customHeight="1">
@@ -3203,33 +3054,33 @@
         <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D59" s="26">
+        <v>63</v>
+      </c>
+      <c r="C59" s="14">
+        <v>1717.1421970722449</v>
+      </c>
+      <c r="D59" s="14"/>
+      <c r="E59" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F59" s="14">
         <v>161.44219707224494</v>
       </c>
-      <c r="E59" s="26"/>
-      <c r="F59" s="26">
-        <v>1717.1421970722449</v>
-      </c>
-      <c r="G59" s="26"/>
+      <c r="G59" s="14"/>
       <c r="H59" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="J59" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L59" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="M59" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="16" customHeight="1">
@@ -3237,21 +3088,21 @@
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D60" s="26">
+        <v>63</v>
+      </c>
+      <c r="C60" s="14">
+        <v>1716.1229098926863</v>
+      </c>
+      <c r="D60" s="14"/>
+      <c r="E60" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F60" s="14">
         <v>160.42290989268619</v>
       </c>
-      <c r="E60" s="26"/>
-      <c r="F60" s="26">
-        <v>1716.1229098926863</v>
-      </c>
-      <c r="G60" s="26"/>
+      <c r="G60" s="14"/>
       <c r="P60" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="16" customHeight="1">
@@ -3259,33 +3110,33 @@
         <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D61" s="26">
+        <v>63</v>
+      </c>
+      <c r="C61" s="14">
+        <v>1669.5217446517536</v>
+      </c>
+      <c r="D61" s="14"/>
+      <c r="E61" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" s="14">
         <v>113.82174465175345</v>
       </c>
-      <c r="E61" s="26"/>
-      <c r="F61" s="26">
-        <v>1669.5217446517536</v>
-      </c>
-      <c r="G61" s="26"/>
+      <c r="G61" s="14"/>
       <c r="H61" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J61" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L61" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="M61" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="16" customHeight="1">
@@ -3293,21 +3144,21 @@
         <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D62" s="26">
+        <v>63</v>
+      </c>
+      <c r="C62" s="14">
+        <v>1668.5024574721947</v>
+      </c>
+      <c r="D62" s="14"/>
+      <c r="E62" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F62" s="14">
         <v>112.8024574721947</v>
       </c>
-      <c r="E62" s="26"/>
-      <c r="F62" s="26">
-        <v>1668.5024574721947</v>
-      </c>
-      <c r="G62" s="26"/>
+      <c r="G62" s="14"/>
       <c r="P62" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="16" customHeight="1">
@@ -3315,27 +3166,27 @@
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D63" s="26">
+        <v>63</v>
+      </c>
+      <c r="C63" s="14">
+        <v>1659.8485884536485</v>
+      </c>
+      <c r="D63" s="14"/>
+      <c r="E63" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F63" s="14">
         <v>104.14858845364853</v>
       </c>
-      <c r="E63" s="26"/>
-      <c r="F63" s="26">
-        <v>1659.8485884536485</v>
-      </c>
-      <c r="G63" s="26"/>
+      <c r="G63" s="14"/>
       <c r="L63" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="M63" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="P63" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="16" customHeight="1">
@@ -3343,27 +3194,27 @@
         <v>62</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D64" s="26">
+        <v>63</v>
+      </c>
+      <c r="C64" s="14">
+        <v>1658.8293012740899</v>
+      </c>
+      <c r="D64" s="14"/>
+      <c r="E64" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F64" s="14">
         <v>103.12930127408978</v>
       </c>
-      <c r="E64" s="26"/>
-      <c r="F64" s="26">
-        <v>1658.8293012740899</v>
-      </c>
-      <c r="G64" s="26"/>
+      <c r="G64" s="14"/>
       <c r="H64" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J64" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:16" ht="16" customHeight="1">
@@ -3371,21 +3222,21 @@
         <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D65" s="26">
+        <v>63</v>
+      </c>
+      <c r="C65" s="14">
+        <v>1655.001938346893</v>
+      </c>
+      <c r="D65" s="14"/>
+      <c r="E65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F65" s="14">
         <v>99.301938346892925</v>
       </c>
-      <c r="E65" s="26"/>
-      <c r="F65" s="26">
-        <v>1655.001938346893</v>
-      </c>
-      <c r="G65" s="26"/>
+      <c r="G65" s="14"/>
       <c r="P65" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:16" ht="16" customHeight="1">
@@ -3393,27 +3244,27 @@
         <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D66" s="26">
+        <v>63</v>
+      </c>
+      <c r="C66" s="14">
+        <v>1650.9610488563894</v>
+      </c>
+      <c r="D66" s="14"/>
+      <c r="E66" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F66" s="14">
         <v>95.261048856389294</v>
       </c>
-      <c r="E66" s="26"/>
-      <c r="F66" s="26">
-        <v>1650.9610488563894</v>
-      </c>
-      <c r="G66" s="26"/>
+      <c r="G66" s="14"/>
       <c r="L66" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="M66" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="16" customHeight="1">
@@ -3421,27 +3272,27 @@
         <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D67" s="26">
+        <v>63</v>
+      </c>
+      <c r="C67" s="14">
+        <v>1637.2550607739433</v>
+      </c>
+      <c r="D67" s="14"/>
+      <c r="E67" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F67" s="14">
         <v>81.555060773943268</v>
       </c>
-      <c r="E67" s="26"/>
-      <c r="F67" s="26">
-        <v>1637.2550607739433</v>
-      </c>
-      <c r="G67" s="26"/>
+      <c r="G67" s="14"/>
       <c r="L67" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M67" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="16" customHeight="1">
@@ -3449,33 +3300,33 @@
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D68" s="26">
+        <v>63</v>
+      </c>
+      <c r="C68" s="14">
+        <v>1627.0662177814372</v>
+      </c>
+      <c r="D68" s="14"/>
+      <c r="E68" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F68" s="14">
         <v>71.366217781437086</v>
       </c>
-      <c r="E68" s="26"/>
-      <c r="F68" s="26">
-        <v>1627.0662177814372</v>
-      </c>
-      <c r="G68" s="26"/>
+      <c r="G68" s="14"/>
       <c r="H68" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="J68" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="M68" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="16" customHeight="1">
@@ -3483,24 +3334,24 @@
         <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D69" s="26">
+        <v>63</v>
+      </c>
+      <c r="C69" s="14">
+        <v>1625.9502393279281</v>
+      </c>
+      <c r="D69" s="14"/>
+      <c r="E69" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F69" s="14">
         <v>70.250239327928099</v>
       </c>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26">
-        <v>1625.9502393279281</v>
-      </c>
-      <c r="G69" s="26"/>
+      <c r="G69" s="14"/>
       <c r="L69" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="16" customHeight="1">
@@ -3508,37 +3359,37 @@
         <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D70" s="26">
+        <v>63</v>
+      </c>
+      <c r="C70" s="14">
+        <v>1613.5052666099164</v>
+      </c>
+      <c r="D70" s="14">
+        <v>1624.4152653539682</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F70" s="14">
         <v>57.805266609916409</v>
       </c>
-      <c r="E70" s="26">
+      <c r="G70" s="14">
         <v>68.715265353968093</v>
       </c>
-      <c r="F70" s="26">
-        <v>1613.5052666099164</v>
-      </c>
-      <c r="G70" s="26">
-        <v>1624.4152653539682</v>
-      </c>
       <c r="H70" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="J70" t="s">
-        <v>175</v>
-      </c>
-      <c r="L70" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="M70" s="31" t="s">
-        <v>205</v>
+        <v>172</v>
+      </c>
+      <c r="L70" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="M70" s="19" t="s">
+        <v>202</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="16" customHeight="1">
@@ -3546,27 +3397,27 @@
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D71" s="26">
+        <v>63</v>
+      </c>
+      <c r="C71" s="14">
+        <v>1601.064322694986</v>
+      </c>
+      <c r="D71" s="14"/>
+      <c r="E71" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F71" s="14">
         <v>45.364322694985972</v>
       </c>
-      <c r="E71" s="26"/>
-      <c r="F71" s="26">
-        <v>1601.064322694986</v>
-      </c>
-      <c r="G71" s="26"/>
+      <c r="G71" s="14"/>
       <c r="L71" t="s">
-        <v>208</v>
-      </c>
-      <c r="M71" s="31" t="s">
-        <v>207</v>
+        <v>205</v>
+      </c>
+      <c r="M71" s="19" t="s">
+        <v>204</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="16" customHeight="1">
@@ -3574,24 +3425,24 @@
         <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72" s="26">
+        <v>63</v>
+      </c>
+      <c r="C72" s="14">
+        <v>1581.4561380984942</v>
+      </c>
+      <c r="D72" s="14"/>
+      <c r="E72" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F72" s="14">
         <v>25.756138098494258</v>
       </c>
-      <c r="E72" s="26"/>
-      <c r="F72" s="26">
-        <v>1581.4561380984942</v>
-      </c>
-      <c r="G72" s="26"/>
+      <c r="G72" s="14"/>
       <c r="L72" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="16" customHeight="1">
@@ -3599,24 +3450,24 @@
         <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D73" s="26">
+        <v>63</v>
+      </c>
+      <c r="C73" s="14">
+        <v>1578.8817329295694</v>
+      </c>
+      <c r="D73" s="14"/>
+      <c r="E73" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F73" s="14">
         <v>23.181732929569211</v>
       </c>
-      <c r="E73" s="26"/>
-      <c r="F73" s="26">
-        <v>1578.8817329295694</v>
-      </c>
-      <c r="G73" s="26"/>
-      <c r="L73" s="31" t="s">
-        <v>209</v>
+      <c r="G73" s="14"/>
+      <c r="L73" s="19" t="s">
+        <v>206</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="16" customHeight="1">
@@ -3624,25 +3475,25 @@
         <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D74" s="26">
+        <v>63</v>
+      </c>
+      <c r="C74" s="14">
+        <v>1563.4473883252626</v>
+      </c>
+      <c r="D74" s="14"/>
+      <c r="E74" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F74" s="14">
         <v>7.7473883252627029</v>
       </c>
-      <c r="E74" s="26"/>
-      <c r="F74" s="26">
-        <v>1563.4473883252626</v>
-      </c>
-      <c r="G74" s="26"/>
-      <c r="L74" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="M74" s="31"/>
+      <c r="G74" s="14"/>
+      <c r="L74" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="M74" s="19"/>
       <c r="P74" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="16" customHeight="1">
@@ -3650,30 +3501,30 @@
         <v>73</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="D75" s="26">
+        <v>63</v>
+      </c>
+      <c r="C75" s="14">
+        <v>1555.7</v>
+      </c>
+      <c r="D75" s="14"/>
+      <c r="E75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F75" s="14">
         <v>0</v>
       </c>
-      <c r="E75" s="26"/>
-      <c r="F75" s="26">
-        <v>1555.7</v>
-      </c>
-      <c r="G75" s="26"/>
+      <c r="G75" s="14"/>
       <c r="H75" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="16" customHeight="1">
@@ -3681,29 +3532,29 @@
         <v>74</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D76" s="26">
+        <v>63</v>
+      </c>
+      <c r="C76" s="14">
+        <v>1548.190979110748</v>
+      </c>
+      <c r="D76" s="14"/>
+      <c r="E76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F76" s="14">
         <v>19.390979110748045</v>
       </c>
-      <c r="E76" s="29">
+      <c r="G76" s="17">
         <v>26.9</v>
       </c>
-      <c r="F76" s="26">
-        <v>1548.190979110748</v>
-      </c>
-      <c r="G76" s="26"/>
       <c r="J76" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M76" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="16" customHeight="1">
@@ -3711,21 +3562,21 @@
         <v>75</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D77" s="26">
+        <v>63</v>
+      </c>
+      <c r="C77" s="14">
+        <v>1547.5631345547904</v>
+      </c>
+      <c r="D77" s="14"/>
+      <c r="E77" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F77" s="14">
         <v>18.763134554790525</v>
       </c>
-      <c r="E77" s="26"/>
-      <c r="F77" s="26">
-        <v>1547.5631345547904</v>
-      </c>
-      <c r="G77" s="26"/>
+      <c r="G77" s="14"/>
       <c r="P77" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="16" customHeight="1">
@@ -3733,21 +3584,21 @@
         <v>76</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D78" s="26">
+        <v>63</v>
+      </c>
+      <c r="C78" s="14">
+        <v>1544.7723655035593</v>
+      </c>
+      <c r="D78" s="14"/>
+      <c r="E78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F78" s="14">
         <v>15.972365503559343</v>
       </c>
-      <c r="E78" s="26"/>
-      <c r="F78" s="26">
-        <v>1544.7723655035593</v>
-      </c>
-      <c r="G78" s="26"/>
+      <c r="G78" s="14"/>
       <c r="P78" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="16" customHeight="1">
@@ -3755,24 +3606,24 @@
         <v>77</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C79" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="D79" s="26">
+        <v>63</v>
+      </c>
+      <c r="C79" s="14">
+        <v>1540.9927412766949</v>
+      </c>
+      <c r="D79" s="14"/>
+      <c r="E79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F79" s="14">
         <v>12.192741276695065</v>
       </c>
-      <c r="E79" s="26"/>
-      <c r="F79" s="26">
-        <v>1540.9927412766949</v>
-      </c>
-      <c r="G79" s="26"/>
+      <c r="G79" s="14"/>
       <c r="M79" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="16" customHeight="1">
@@ -3780,30 +3631,30 @@
         <v>78</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C80" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="14">
+        <v>1528.8</v>
+      </c>
+      <c r="D80" s="14"/>
+      <c r="E80" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F80" s="14">
+        <v>0</v>
+      </c>
+      <c r="G80" s="14"/>
+      <c r="H80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L80" s="19" t="s">
+        <v>210</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="P80" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="D80" s="26">
-        <v>0</v>
-      </c>
-      <c r="E80" s="26"/>
-      <c r="F80" s="26">
-        <v>1528.8</v>
-      </c>
-      <c r="G80" s="26"/>
-      <c r="H80" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L80" s="31" t="s">
-        <v>213</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="P80" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="16" customHeight="1">
@@ -3811,29 +3662,29 @@
         <v>79</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C81" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D81" s="26">
+        <v>63</v>
+      </c>
+      <c r="C81" s="14">
+        <v>1514.0251166407463</v>
+      </c>
+      <c r="D81" s="14"/>
+      <c r="E81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F81" s="14">
         <v>9.1251166407464996</v>
       </c>
-      <c r="E81" s="29">
+      <c r="G81" s="17">
         <v>23.9</v>
       </c>
-      <c r="F81" s="26">
-        <v>1514.0251166407463</v>
-      </c>
-      <c r="G81" s="26"/>
       <c r="J81" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M81" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="16" customHeight="1">
@@ -3841,21 +3692,21 @@
         <v>80</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D82" s="26">
+        <v>63</v>
+      </c>
+      <c r="C82" s="14">
+        <v>1512.826399688958</v>
+      </c>
+      <c r="D82" s="14"/>
+      <c r="E82" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F82" s="14">
         <v>7.9263996889580088</v>
       </c>
-      <c r="E82" s="26"/>
-      <c r="F82" s="26">
-        <v>1512.826399688958</v>
-      </c>
-      <c r="G82" s="26"/>
+      <c r="G82" s="14"/>
       <c r="P82" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="16" customHeight="1">
@@ -3863,33 +3714,33 @@
         <v>81</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D83" s="26">
+        <v>63</v>
+      </c>
+      <c r="C83" s="14">
+        <v>1506.0088906168999</v>
+      </c>
+      <c r="D83" s="14"/>
+      <c r="E83" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F83" s="14">
         <v>1.1088906168999482</v>
       </c>
-      <c r="E83" s="26"/>
-      <c r="F83" s="26">
-        <v>1506.0088906168999</v>
-      </c>
-      <c r="G83" s="26"/>
+      <c r="G83" s="14"/>
       <c r="H83" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J83" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="L83" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="M83" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P83" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="16" customHeight="1">
@@ -3897,33 +3748,33 @@
         <v>82</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D84" s="26">
+        <v>63</v>
+      </c>
+      <c r="C84" s="14">
+        <v>1504.8999999999999</v>
+      </c>
+      <c r="D84" s="14"/>
+      <c r="E84" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F84" s="14">
         <v>0</v>
       </c>
-      <c r="E84" s="26"/>
-      <c r="F84" s="26">
-        <v>1504.8999999999999</v>
-      </c>
-      <c r="G84" s="26"/>
+      <c r="G84" s="14"/>
       <c r="H84" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="L84" s="31" t="s">
-        <v>216</v>
+        <v>174</v>
+      </c>
+      <c r="L84" s="19" t="s">
+        <v>213</v>
       </c>
       <c r="M84" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P84" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85" spans="1:16" ht="16" customHeight="1">
@@ -3931,32 +3782,32 @@
         <v>83</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C85" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D85" s="26">
+        <v>63</v>
+      </c>
+      <c r="C85" s="14">
+        <v>1487.7601934415752</v>
+      </c>
+      <c r="D85" s="14"/>
+      <c r="E85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F85" s="14">
         <v>229.56019344157539</v>
       </c>
-      <c r="E85">
+      <c r="G85">
         <v>246.7</v>
       </c>
-      <c r="F85" s="26">
-        <v>1487.7601934415752</v>
-      </c>
-      <c r="G85" s="26"/>
       <c r="J85" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L85" t="s">
-        <v>216</v>
-      </c>
-      <c r="M85" s="31" t="s">
-        <v>216</v>
+        <v>213</v>
+      </c>
+      <c r="M85" s="19" t="s">
+        <v>213</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:16" ht="16" customHeight="1">
@@ -3964,27 +3815,27 @@
         <v>84</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D86" s="26">
+        <v>63</v>
+      </c>
+      <c r="C86" s="14">
+        <v>1483.1456301373839</v>
+      </c>
+      <c r="D86" s="14"/>
+      <c r="E86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F86" s="14">
         <v>224.94563013738417</v>
       </c>
-      <c r="E86" s="26"/>
-      <c r="F86" s="26">
-        <v>1483.1456301373839</v>
-      </c>
-      <c r="G86" s="26"/>
-      <c r="L86" s="31" t="s">
-        <v>217</v>
+      <c r="G86" s="14"/>
+      <c r="L86" s="19" t="s">
+        <v>214</v>
       </c>
       <c r="M86" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:16" ht="16" customHeight="1">
@@ -3992,24 +3843,24 @@
         <v>85</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D87" s="26">
+        <v>63</v>
+      </c>
+      <c r="C87" s="14">
+        <v>1468.6176377472477</v>
+      </c>
+      <c r="D87" s="14"/>
+      <c r="E87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F87" s="14">
         <v>210.41763774724797</v>
       </c>
-      <c r="E87" s="26"/>
-      <c r="F87" s="26">
-        <v>1468.6176377472477</v>
-      </c>
-      <c r="G87" s="26"/>
+      <c r="G87" s="14"/>
       <c r="L87" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:16" ht="16" customHeight="1">
@@ -4017,24 +3868,24 @@
         <v>86</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D88" s="26">
+        <v>63</v>
+      </c>
+      <c r="C88" s="14">
+        <v>1467.1630471404919</v>
+      </c>
+      <c r="D88" s="14"/>
+      <c r="E88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F88" s="14">
         <v>208.96304714049202</v>
       </c>
-      <c r="E88" s="26"/>
-      <c r="F88" s="26">
-        <v>1467.1630471404919</v>
-      </c>
-      <c r="G88" s="26"/>
+      <c r="G88" s="14"/>
       <c r="L88" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="89" spans="1:16" ht="16" customHeight="1">
@@ -4042,25 +3893,25 @@
         <v>87</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D89" s="26">
+        <v>63</v>
+      </c>
+      <c r="C89" s="14">
+        <v>1457.1707978738852</v>
+      </c>
+      <c r="D89" s="14"/>
+      <c r="E89" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F89" s="14">
         <v>198.97079787388537</v>
       </c>
-      <c r="E89" s="26"/>
-      <c r="F89" s="26">
-        <v>1457.1707978738852</v>
-      </c>
-      <c r="G89" s="26"/>
+      <c r="G89" s="14"/>
       <c r="L89" t="s">
-        <v>218</v>
-      </c>
-      <c r="M89" s="31"/>
+        <v>215</v>
+      </c>
+      <c r="M89" s="19"/>
       <c r="P89" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:16" ht="16" customHeight="1">
@@ -4068,21 +3919,21 @@
         <v>88</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D90" s="26">
+        <v>63</v>
+      </c>
+      <c r="C90" s="14">
+        <v>1432.0486566557261</v>
+      </c>
+      <c r="D90" s="14"/>
+      <c r="E90" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F90" s="14">
         <v>173.84865665572627</v>
       </c>
-      <c r="E90" s="26"/>
-      <c r="F90" s="26">
-        <v>1432.0486566557261</v>
-      </c>
-      <c r="G90" s="26"/>
+      <c r="G90" s="14"/>
       <c r="P90" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="91" spans="1:16" ht="16" customHeight="1">
@@ -4090,21 +3941,21 @@
         <v>89</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D91" s="26">
+        <v>63</v>
+      </c>
+      <c r="C91" s="14">
+        <v>1410.9785892706727</v>
+      </c>
+      <c r="D91" s="14"/>
+      <c r="E91" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F91" s="14">
         <v>152.77858927067297</v>
       </c>
-      <c r="E91" s="26"/>
-      <c r="F91" s="26">
-        <v>1410.9785892706727</v>
-      </c>
-      <c r="G91" s="26"/>
+      <c r="G91" s="14"/>
       <c r="P91" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:16" ht="16" customHeight="1">
@@ -4112,21 +3963,21 @@
         <v>90</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D92" s="26">
+        <v>63</v>
+      </c>
+      <c r="C92" s="14">
+        <v>1409.4917540445554</v>
+      </c>
+      <c r="D92" s="14"/>
+      <c r="E92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F92" s="14">
         <v>151.29175404455546</v>
       </c>
-      <c r="E92" s="26"/>
-      <c r="F92" s="26">
-        <v>1409.4917540445554</v>
-      </c>
-      <c r="G92" s="26"/>
+      <c r="G92" s="14"/>
       <c r="P92" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:16" ht="16" customHeight="1">
@@ -4134,33 +3985,33 @@
         <v>91</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D93" s="26">
+        <v>63</v>
+      </c>
+      <c r="C93" s="14">
+        <v>1353.5115120973596</v>
+      </c>
+      <c r="D93" s="14"/>
+      <c r="E93" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F93" s="14">
         <v>95.311512097359781</v>
       </c>
-      <c r="E93" s="26"/>
-      <c r="F93" s="26">
-        <v>1353.5115120973596</v>
-      </c>
-      <c r="G93" s="26"/>
+      <c r="G93" s="14"/>
       <c r="H93" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="J93" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L93" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="M93" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94" spans="1:16" ht="16" customHeight="1">
@@ -4168,25 +4019,25 @@
         <v>92</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C94" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D94" s="26">
+        <v>63</v>
+      </c>
+      <c r="C94" s="14">
+        <v>1323.1621598071392</v>
+      </c>
+      <c r="D94" s="14">
+        <v>1349.2695532835689</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F94" s="14">
         <v>64.962159807139329</v>
       </c>
-      <c r="E94" s="26">
+      <c r="G94" s="14">
         <v>91.069553283569078</v>
       </c>
-      <c r="F94" s="26">
-        <v>1323.1621598071392</v>
-      </c>
-      <c r="G94" s="26">
-        <v>1349.2695532835689</v>
-      </c>
       <c r="P94" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="95" spans="1:16" ht="16" customHeight="1">
@@ -4194,21 +4045,21 @@
         <v>93</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C95" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D95" s="26">
+        <v>63</v>
+      </c>
+      <c r="C95" s="14">
+        <v>1321.7075692003832</v>
+      </c>
+      <c r="D95" s="14"/>
+      <c r="E95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F95" s="14">
         <v>63.507569200383394</v>
       </c>
-      <c r="E95" s="26"/>
-      <c r="F95" s="26">
-        <v>1321.7075692003832</v>
-      </c>
-      <c r="G95" s="26"/>
+      <c r="G95" s="14"/>
       <c r="P95" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="96" spans="1:16" ht="16" customHeight="1">
@@ -4216,24 +4067,24 @@
         <v>94</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D96" s="26">
+        <v>63</v>
+      </c>
+      <c r="C96" s="14">
+        <v>1277.8154767782971</v>
+      </c>
+      <c r="D96" s="14"/>
+      <c r="E96" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F96" s="14">
         <v>19.615476778297364</v>
       </c>
-      <c r="E96" s="26"/>
-      <c r="F96" s="26">
-        <v>1277.8154767782971</v>
-      </c>
-      <c r="G96" s="26"/>
+      <c r="G96" s="14"/>
       <c r="M96" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="16" customHeight="1">
@@ -4241,24 +4092,24 @@
         <v>95</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C97" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D97" s="26">
+        <v>63</v>
+      </c>
+      <c r="C97" s="14">
+        <v>1275.2251590229166</v>
+      </c>
+      <c r="D97" s="14"/>
+      <c r="E97" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F97" s="14">
         <v>17.025159022916725</v>
       </c>
-      <c r="E97" s="26"/>
-      <c r="F97" s="26">
-        <v>1275.2251590229166</v>
-      </c>
-      <c r="G97" s="26"/>
+      <c r="G97" s="14"/>
       <c r="L97" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98" spans="1:19" ht="16" customHeight="1">
@@ -4266,37 +4117,37 @@
         <v>96</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D98" s="26">
+        <v>63</v>
+      </c>
+      <c r="C98" s="14">
+        <v>1258.1999999999998</v>
+      </c>
+      <c r="D98" s="14">
+        <v>1271.7857329576809</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F98" s="14">
         <v>0</v>
       </c>
-      <c r="E98" s="26">
+      <c r="G98" s="14">
         <v>13.585732957681023</v>
       </c>
-      <c r="F98" s="26">
-        <v>1258.1999999999998</v>
-      </c>
-      <c r="G98" s="26">
-        <v>1271.7857329576809</v>
-      </c>
       <c r="H98" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="L98" s="31" t="s">
-        <v>222</v>
+        <v>175</v>
+      </c>
+      <c r="L98" s="19" t="s">
+        <v>219</v>
       </c>
       <c r="M98" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:19" ht="16" customHeight="1">
@@ -4304,29 +4155,29 @@
         <v>97</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C99" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D99" s="26">
+        <v>63</v>
+      </c>
+      <c r="C99" s="14">
+        <v>1255.6369383328167</v>
+      </c>
+      <c r="D99" s="14"/>
+      <c r="E99" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F99" s="14">
         <v>159.43693833281682</v>
       </c>
-      <c r="E99" s="29">
+      <c r="G99" s="17">
         <v>161.99999999999997</v>
       </c>
-      <c r="F99" s="26">
-        <v>1255.6369383328167</v>
-      </c>
-      <c r="G99" s="26"/>
       <c r="J99" t="s">
-        <v>178</v>
-      </c>
-      <c r="M99" s="31" t="s">
-        <v>222</v>
+        <v>175</v>
+      </c>
+      <c r="M99" s="19" t="s">
+        <v>219</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="100" spans="1:19" ht="16" customHeight="1">
@@ -4334,21 +4185,21 @@
         <v>98</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D100" s="26">
+        <v>63</v>
+      </c>
+      <c r="C100" s="14">
+        <v>1251.9750232414005</v>
+      </c>
+      <c r="D100" s="14"/>
+      <c r="E100" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F100" s="14">
         <v>155.77502324140065</v>
       </c>
-      <c r="E100" s="26"/>
-      <c r="F100" s="26">
-        <v>1251.9750232414005</v>
-      </c>
-      <c r="G100" s="26"/>
+      <c r="G100" s="14"/>
       <c r="P100" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101" spans="1:19" ht="16" customHeight="1">
@@ -4356,27 +4207,27 @@
         <v>99</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D101" s="26">
+        <v>63</v>
+      </c>
+      <c r="C101" s="14">
+        <v>1249.5263092655714</v>
+      </c>
+      <c r="D101" s="14"/>
+      <c r="E101" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F101" s="14">
         <v>153.32630926557169</v>
       </c>
-      <c r="E101" s="26"/>
-      <c r="F101" s="26">
-        <v>1249.5263092655714</v>
-      </c>
-      <c r="G101" s="26"/>
+      <c r="G101" s="14"/>
       <c r="L101" t="s">
-        <v>222</v>
-      </c>
-      <c r="M101" s="31" t="s">
-        <v>222</v>
+        <v>219</v>
+      </c>
+      <c r="M101" s="19" t="s">
+        <v>219</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="102" spans="1:19" ht="16" customHeight="1">
@@ -4384,27 +4235,27 @@
         <v>100</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C102" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D102" s="26">
+        <v>63</v>
+      </c>
+      <c r="C102" s="14">
+        <v>1233.1132321041214</v>
+      </c>
+      <c r="D102" s="14"/>
+      <c r="E102" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F102" s="14">
         <v>136.91323210412145</v>
       </c>
-      <c r="E102" s="26"/>
-      <c r="F102" s="26">
-        <v>1233.1132321041214</v>
-      </c>
-      <c r="G102" s="26"/>
-      <c r="L102" s="31" t="s">
-        <v>223</v>
+      <c r="G102" s="14"/>
+      <c r="L102" s="19" t="s">
+        <v>220</v>
       </c>
       <c r="M102" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103" spans="1:19" ht="16" customHeight="1">
@@ -4412,24 +4263,24 @@
         <v>101</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C103" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D103" s="26">
+        <v>63</v>
+      </c>
+      <c r="C103" s="14">
+        <v>1231.5151533932444</v>
+      </c>
+      <c r="D103" s="14"/>
+      <c r="E103" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F103" s="14">
         <v>135.31515339324449</v>
       </c>
-      <c r="E103" s="26"/>
-      <c r="F103" s="26">
-        <v>1231.5151533932444</v>
-      </c>
-      <c r="G103" s="26"/>
+      <c r="G103" s="14"/>
       <c r="L103" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="104" spans="1:19" ht="16" customHeight="1">
@@ -4437,21 +4288,21 @@
         <v>102</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D104" s="26">
+        <v>63</v>
+      </c>
+      <c r="C104" s="14">
+        <v>1206.9415556244187</v>
+      </c>
+      <c r="D104" s="14"/>
+      <c r="E104" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F104" s="14">
         <v>110.74155562441896</v>
       </c>
-      <c r="E104" s="26"/>
-      <c r="F104" s="26">
-        <v>1206.9415556244187</v>
-      </c>
-      <c r="G104" s="26"/>
+      <c r="G104" s="14"/>
       <c r="P104" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105" spans="1:19" ht="16" customHeight="1">
@@ -4459,21 +4310,21 @@
         <v>103</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D105" s="26">
+        <v>63</v>
+      </c>
+      <c r="C105" s="14">
+        <v>1204.094019212891</v>
+      </c>
+      <c r="D105" s="14"/>
+      <c r="E105" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F105" s="14">
         <v>107.89401921289122</v>
       </c>
-      <c r="E105" s="26"/>
-      <c r="F105" s="26">
-        <v>1204.094019212891</v>
-      </c>
-      <c r="G105" s="26"/>
+      <c r="G105" s="14"/>
       <c r="P105" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="106" spans="1:19" ht="16" customHeight="1">
@@ -4481,27 +4332,27 @@
         <v>104</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D106" s="26">
+        <v>63</v>
+      </c>
+      <c r="C106" s="14">
+        <v>1181.0097303997518</v>
+      </c>
+      <c r="D106" s="14"/>
+      <c r="E106" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F106" s="14">
         <v>84.809730399752084</v>
       </c>
-      <c r="E106" s="26"/>
-      <c r="F106" s="26">
-        <v>1181.0097303997518</v>
-      </c>
-      <c r="G106" s="26"/>
+      <c r="G106" s="14"/>
       <c r="L106" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M106" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:19" ht="16" customHeight="1">
@@ -4509,21 +4360,21 @@
         <v>105</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C107" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D107" s="26">
+        <v>63</v>
+      </c>
+      <c r="C107" s="14">
+        <v>1179.7072823055469</v>
+      </c>
+      <c r="D107" s="14"/>
+      <c r="E107" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F107" s="14">
         <v>83.507282305546937</v>
       </c>
-      <c r="E107" s="26"/>
-      <c r="F107" s="26">
-        <v>1179.7072823055469</v>
-      </c>
-      <c r="G107" s="26"/>
+      <c r="G107" s="14"/>
       <c r="P107" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="108" spans="1:19" ht="16" customHeight="1">
@@ -4531,27 +4382,27 @@
         <v>106</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C108" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D108" s="26">
+        <v>63</v>
+      </c>
+      <c r="C108" s="14">
+        <v>1167.5250697242018</v>
+      </c>
+      <c r="D108" s="14"/>
+      <c r="E108" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F108" s="14">
         <v>71.325069724202038</v>
       </c>
-      <c r="E108" s="26"/>
-      <c r="F108" s="26">
-        <v>1167.5250697242018</v>
-      </c>
-      <c r="G108" s="26"/>
-      <c r="L108" s="31" t="s">
-        <v>225</v>
+      <c r="G108" s="14"/>
+      <c r="L108" s="19" t="s">
+        <v>222</v>
       </c>
       <c r="M108" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="109" spans="1:19" ht="16" customHeight="1">
@@ -4559,31 +4410,31 @@
         <v>107</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D109" s="26">
+        <v>63</v>
+      </c>
+      <c r="C109" s="14">
+        <v>1138.1656027269908</v>
+      </c>
+      <c r="D109" s="14"/>
+      <c r="E109" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F109" s="14">
         <v>41.965602726991008</v>
       </c>
-      <c r="E109" s="26"/>
-      <c r="F109" s="26">
-        <v>1138.1656027269908</v>
-      </c>
-      <c r="G109" s="26"/>
+      <c r="G109" s="14"/>
       <c r="H109" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J109" t="s">
-        <v>178</v>
-      </c>
-      <c r="L109" s="31"/>
-      <c r="M109" s="31" t="s">
-        <v>225</v>
+        <v>175</v>
+      </c>
+      <c r="L109" s="19"/>
+      <c r="M109" s="19" t="s">
+        <v>222</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="16" customHeight="1">
@@ -4591,21 +4442,21 @@
         <v>108</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C110" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D110" s="26">
+        <v>63</v>
+      </c>
+      <c r="C110" s="14">
+        <v>1124.8454911682675</v>
+      </c>
+      <c r="D110" s="14"/>
+      <c r="E110" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F110" s="14">
         <v>28.645491168267736</v>
       </c>
-      <c r="E110" s="26"/>
-      <c r="F110" s="26">
-        <v>1124.8454911682675</v>
-      </c>
-      <c r="G110" s="26"/>
+      <c r="G110" s="14"/>
       <c r="P110" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="16" customHeight="1">
@@ -4613,30 +4464,30 @@
         <v>109</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C111" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D111" s="26">
+        <v>63</v>
+      </c>
+      <c r="C111" s="14">
+        <v>1096.2</v>
+      </c>
+      <c r="D111" s="14"/>
+      <c r="E111" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F111" s="14">
         <v>0</v>
       </c>
-      <c r="E111" s="26"/>
-      <c r="F111" s="26">
-        <v>1096.2</v>
-      </c>
-      <c r="G111" s="26"/>
+      <c r="G111" s="14"/>
       <c r="H111" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S111" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="112" spans="1:19" ht="16" customHeight="1">
@@ -4644,26 +4495,26 @@
         <v>110</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C112" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D112" s="29">
+        <v>63</v>
+      </c>
+      <c r="C112" s="17">
+        <v>1008.5255813953488</v>
+      </c>
+      <c r="D112" s="14"/>
+      <c r="E112" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F112" s="17">
         <v>702.32558139534876</v>
       </c>
-      <c r="E112" s="29">
+      <c r="G112" s="17">
         <v>790</v>
       </c>
-      <c r="F112" s="29">
-        <v>1008.5255813953488</v>
-      </c>
-      <c r="G112" s="26"/>
-      <c r="J112" s="30" t="s">
-        <v>179</v>
+      <c r="J112" s="18" t="s">
+        <v>176</v>
       </c>
       <c r="P112" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="113" spans="1:16" ht="16" customHeight="1">
@@ -4671,23 +4522,23 @@
         <v>111</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D113" s="29">
+        <v>63</v>
+      </c>
+      <c r="C113" s="17">
+        <v>936.11840065279466</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F113" s="17">
         <v>629.91840065279473</v>
       </c>
-      <c r="E113" s="29"/>
-      <c r="F113" s="29">
-        <v>936.11840065279466</v>
-      </c>
-      <c r="M113" s="31" t="s">
-        <v>226</v>
+      <c r="G113" s="17"/>
+      <c r="M113" s="19" t="s">
+        <v>223</v>
       </c>
       <c r="P113" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="114" spans="1:16" ht="16" customHeight="1">
@@ -4695,20 +4546,20 @@
         <v>112</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C114" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D114" s="29">
+        <v>63</v>
+      </c>
+      <c r="C114" s="17">
+        <v>906.20407996736026</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F114" s="17">
         <v>600.00407996736021</v>
       </c>
-      <c r="E114" s="29"/>
-      <c r="F114" s="29">
-        <v>906.20407996736026</v>
-      </c>
+      <c r="G114" s="17"/>
       <c r="P114" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115" spans="1:16" ht="16" customHeight="1">
@@ -4716,23 +4567,23 @@
         <v>113</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D115" s="29">
+        <v>63</v>
+      </c>
+      <c r="C115" s="17">
+        <v>729.85151621335012</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F115" s="17">
         <v>423.65151621335013</v>
       </c>
-      <c r="E115" s="29"/>
-      <c r="F115" s="29">
-        <v>729.85151621335012</v>
-      </c>
-      <c r="M115" s="31" t="s">
-        <v>227</v>
+      <c r="G115" s="17"/>
+      <c r="M115" s="19" t="s">
+        <v>224</v>
       </c>
       <c r="P115" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="116" spans="1:16" ht="16" customHeight="1">
@@ -4740,20 +4591,20 @@
         <v>114</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C116" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D116" s="29">
+        <v>63</v>
+      </c>
+      <c r="C116" s="17">
+        <v>727.06618643247907</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F116" s="17">
         <v>420.86618643247908</v>
       </c>
-      <c r="E116" s="29"/>
-      <c r="F116" s="29">
-        <v>727.06618643247907</v>
-      </c>
+      <c r="G116" s="17"/>
       <c r="P116" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="117" spans="1:16" ht="16" customHeight="1">
@@ -4761,22 +4612,22 @@
         <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C117" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D117" s="29">
+        <v>63</v>
+      </c>
+      <c r="C117" s="17">
+        <v>706.14154938174772</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F117" s="17">
         <v>399.94154938174773</v>
       </c>
-      <c r="E117" s="29">
+      <c r="G117" s="17">
         <v>408.47289623618741</v>
       </c>
-      <c r="F117" s="29">
-        <v>706.14154938174772</v>
-      </c>
       <c r="P117" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118" spans="1:16" ht="16" customHeight="1">
@@ -4784,23 +4635,23 @@
         <v>116</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D118" s="29">
+        <v>63</v>
+      </c>
+      <c r="C118" s="17">
+        <v>606.20407996736026</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F118" s="17">
         <v>300.00407996736027</v>
       </c>
-      <c r="E118" s="29"/>
-      <c r="F118" s="29">
-        <v>606.20407996736026</v>
-      </c>
-      <c r="M118" s="31" t="s">
-        <v>228</v>
+      <c r="G118" s="17"/>
+      <c r="M118" s="19" t="s">
+        <v>225</v>
       </c>
       <c r="P118" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="119" spans="1:16" ht="16" customHeight="1">
@@ -4808,20 +4659,20 @@
         <v>117</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D119" s="29">
+        <v>63</v>
+      </c>
+      <c r="C119" s="17">
+        <v>417.01191350469196</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F119" s="17">
         <v>110.81191350469196</v>
       </c>
-      <c r="E119" s="29"/>
-      <c r="F119" s="29">
-        <v>417.01191350469196</v>
-      </c>
+      <c r="G119" s="17"/>
       <c r="P119" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="120" spans="1:16" ht="16" customHeight="1">
@@ -4829,20 +4680,20 @@
         <v>118</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D120" s="29">
+        <v>63</v>
+      </c>
+      <c r="C120" s="17">
+        <v>408.92541819665439</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F120" s="17">
         <v>102.72541819665442</v>
       </c>
-      <c r="E120" s="29"/>
-      <c r="F120" s="29">
-        <v>408.92541819665439</v>
-      </c>
+      <c r="G120" s="17"/>
       <c r="P120" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121" spans="1:16" ht="16" customHeight="1">
@@ -4850,20 +4701,20 @@
         <v>119</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C121" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D121" s="29">
+        <v>63</v>
+      </c>
+      <c r="C121" s="17">
+        <v>334.4986536107711</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F121" s="17">
         <v>28.298653610771115</v>
       </c>
-      <c r="E121" s="29"/>
-      <c r="F121" s="29">
-        <v>334.4986536107711</v>
-      </c>
+      <c r="G121" s="17"/>
       <c r="P121" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="122" spans="1:16" ht="16" customHeight="1">
@@ -4871,20 +4722,20 @@
         <v>120</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C122" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D122" s="29">
+        <v>63</v>
+      </c>
+      <c r="C122" s="17">
+        <v>325.06576907384738</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F122" s="17">
         <v>18.86576907384741</v>
       </c>
-      <c r="E122" s="29"/>
-      <c r="F122" s="29">
-        <v>325.06576907384738</v>
-      </c>
+      <c r="G122" s="17"/>
       <c r="P122" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="123" spans="1:16" ht="16" customHeight="1">
@@ -4892,29 +4743,29 @@
         <v>121</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D123" s="29">
+        <v>63</v>
+      </c>
+      <c r="C123" s="17">
+        <v>306.2</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F123" s="17">
         <v>0</v>
       </c>
-      <c r="E123" s="29"/>
-      <c r="F123" s="29">
-        <v>306.2</v>
-      </c>
+      <c r="G123" s="17"/>
       <c r="H123" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I123" s="1">
         <v>0</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P123" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="124" spans="1:16" ht="16">
@@ -4922,29 +4773,29 @@
         <v>122</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C124" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D124" s="26">
+        <v>63</v>
+      </c>
+      <c r="C124" s="14">
+        <v>285.60862979114103</v>
+      </c>
+      <c r="D124" s="14"/>
+      <c r="E124" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F124" s="14">
         <v>285.60862979114069</v>
       </c>
-      <c r="E124" s="26">
+      <c r="G124" s="14">
         <v>306.2</v>
       </c>
-      <c r="F124" s="26">
-        <v>285.60862979114103</v>
-      </c>
-      <c r="G124" s="26"/>
       <c r="J124" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K124">
         <v>1</v>
       </c>
       <c r="P124" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="125" spans="1:16" ht="16">
@@ -4952,21 +4803,21 @@
         <v>123</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D125" s="26">
+        <v>63</v>
+      </c>
+      <c r="C125" s="14">
         <v>276.57794353913243</v>
       </c>
-      <c r="E125" s="26"/>
-      <c r="F125" s="26">
+      <c r="D125" s="14"/>
+      <c r="E125" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F125" s="14">
         <v>276.57794353913243</v>
       </c>
-      <c r="G125" s="26"/>
+      <c r="G125" s="14"/>
       <c r="P125" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="126" spans="1:16" ht="16">
@@ -4974,21 +4825,21 @@
         <v>124</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D126" s="26">
+        <v>63</v>
+      </c>
+      <c r="C126" s="14">
         <v>230.81153444010917</v>
       </c>
-      <c r="E126" s="26"/>
-      <c r="F126" s="26">
+      <c r="D126" s="14"/>
+      <c r="E126" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F126" s="14">
         <v>230.81153444010917</v>
       </c>
-      <c r="G126" s="26"/>
+      <c r="G126" s="14"/>
       <c r="P126" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="127" spans="1:16" ht="16">
@@ -4996,30 +4847,30 @@
         <v>125</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D127" s="26">
+        <v>63</v>
+      </c>
+      <c r="C127" s="14">
         <v>215.68230433784717</v>
       </c>
-      <c r="E127" s="26"/>
-      <c r="F127" s="26">
+      <c r="D127" s="14"/>
+      <c r="E127" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F127" s="14">
         <v>215.68230433784717</v>
       </c>
-      <c r="G127" s="26"/>
+      <c r="G127" s="14"/>
       <c r="H127" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="M127" s="31" t="s">
-        <v>229</v>
+        <v>178</v>
+      </c>
+      <c r="M127" s="19" t="s">
+        <v>226</v>
       </c>
       <c r="P127" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:16" ht="16">
@@ -5027,21 +4878,21 @@
         <v>126</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C128" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D128" s="26">
+        <v>63</v>
+      </c>
+      <c r="C128" s="14">
         <v>204.45348736388445</v>
       </c>
-      <c r="E128" s="26"/>
-      <c r="F128" s="26">
+      <c r="D128" s="14"/>
+      <c r="E128" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F128" s="14">
         <v>204.45348736388445</v>
       </c>
-      <c r="G128" s="26"/>
+      <c r="G128" s="14"/>
       <c r="P128" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="129" spans="1:19" ht="16">
@@ -5049,21 +4900,21 @@
         <v>127</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D129" s="26">
+        <v>63</v>
+      </c>
+      <c r="C129" s="14">
         <v>183.57319766404001</v>
       </c>
-      <c r="E129" s="26"/>
-      <c r="F129" s="26">
+      <c r="D129" s="14"/>
+      <c r="E129" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F129" s="14">
         <v>183.57319766404001</v>
       </c>
-      <c r="G129" s="26"/>
+      <c r="G129" s="14"/>
       <c r="P129" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:19" ht="16">
@@ -5071,21 +4922,21 @@
         <v>128</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D130" s="26">
+        <v>63</v>
+      </c>
+      <c r="C130" s="14">
         <v>177.38875882997988</v>
       </c>
-      <c r="E130" s="26"/>
-      <c r="F130" s="26">
+      <c r="D130" s="14"/>
+      <c r="E130" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F130" s="14">
         <v>177.38875882997988</v>
       </c>
-      <c r="G130" s="26"/>
+      <c r="G130" s="14"/>
       <c r="P130" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="131" spans="1:19" ht="16">
@@ -5093,21 +4944,21 @@
         <v>129</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C131" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D131" s="26">
+        <v>63</v>
+      </c>
+      <c r="C131" s="14">
         <v>168.04963149975777</v>
       </c>
-      <c r="E131" s="26"/>
-      <c r="F131" s="26">
+      <c r="D131" s="14"/>
+      <c r="E131" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F131" s="14">
         <v>168.04963149975777</v>
       </c>
-      <c r="G131" s="26"/>
+      <c r="G131" s="14"/>
       <c r="P131" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="132" spans="1:19" ht="16">
@@ -5115,21 +4966,21 @@
         <v>130</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D132" s="26">
+        <v>63</v>
+      </c>
+      <c r="C132" s="14">
         <v>162.74366409099025</v>
       </c>
-      <c r="E132" s="26"/>
-      <c r="F132" s="26">
+      <c r="D132" s="14"/>
+      <c r="E132" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F132" s="14">
         <v>162.74366409099025</v>
       </c>
-      <c r="G132" s="26"/>
+      <c r="G132" s="14"/>
       <c r="P132" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:19" ht="16">
@@ -5137,27 +4988,27 @@
         <v>131</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C133" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D133" s="26">
+        <v>63</v>
+      </c>
+      <c r="C133" s="14">
         <v>147.07173386376968</v>
       </c>
-      <c r="E133" s="26"/>
-      <c r="F133" s="26">
+      <c r="D133" s="14"/>
+      <c r="E133" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F133" s="14">
         <v>147.07173386376968</v>
       </c>
-      <c r="G133" s="26"/>
+      <c r="G133" s="14"/>
       <c r="O133" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P133" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S133" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="134" spans="1:19" ht="16">
@@ -5165,29 +5016,29 @@
         <v>132</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C134" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D134" s="26">
+        <v>63</v>
+      </c>
+      <c r="C134" s="14">
         <v>0</v>
       </c>
-      <c r="E134" s="26"/>
-      <c r="F134" s="26">
+      <c r="D134" s="14"/>
+      <c r="E134" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F134" s="14">
         <v>0</v>
       </c>
-      <c r="G134" s="26"/>
+      <c r="G134" s="14"/>
       <c r="H134" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="O134" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:A123" xr:uid="{A28FFD51-ADBD-449D-82B6-FD1C9C527D60}"/>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <conditionalFormatting sqref="O1">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>ISEVEN(#REF!)</formula>
@@ -5223,392 +5074,388 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16">
       <c r="A1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="C1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="D1" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="E1" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>110</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="224" customHeight="1">
       <c r="A2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="110" customHeight="1">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="80" customHeight="1">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="139" customHeight="1">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I5" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="109" customHeight="1">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J6" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K6" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="110" customHeight="1">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I7" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>129</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="112">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="123" customHeight="1">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="126" customHeight="1">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>248</v>
-      </c>
       <c r="I10" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="K10" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>140</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="13" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{657615FF-0968-7A44-B4C7-56243043F48A}">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" customWidth="1"/>
-    <col min="6" max="6" width="12.5" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.33203125" customWidth="1"/>
+    <col min="5" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:14">
+      <c r="A1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
         <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N1" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="O1" s="6"/>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="K1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="5"/>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>149</v>
+      </c>
+      <c r="C2" t="s">
+        <v>248</v>
       </c>
       <c r="D2" t="s">
-        <v>251</v>
+        <v>148</v>
       </c>
       <c r="E2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K2" t="s">
         <v>249</v>
       </c>
-      <c r="H2" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" t="s">
-        <v>163</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINESTRING(-135.58285 65.884392, -135.614518 65.874512, -135.590261 65.881752, -135.614518 65.874512, -135.63898 65.876358, -135.646407 65.875853, -135.66724 65.873555, -135.666052 65.873173, -135.66813 65.873029, -135.667378 65.873898, -135.669039 65.872632, -135.709033 65.880767, -135.74485 65.877133, -135.745033 65.877033, -135.764983 65.876483, -135.748317 65.876483, -135.759983 65.872133, -135.754891 65.869714, -135.761648 65.867955, -135.763178 65.86773, -135.845633 65.866017)</t>
-        </is>
-      </c>
-      <c r="N2" t="s">
-        <v>153</v>
+      <c r="M2" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -5628,57 +5475,57 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>23</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>24</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>27</v>
       </c>
-      <c r="F1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" t="s">
-        <v>28</v>
-      </c>
       <c r="J1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C2" s="27" t="s">
-        <v>155</v>
+        <v>151</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>152</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="G2">
         <v>2020</v>
       </c>
-      <c r="H2" s="28" t="s">
-        <v>157</v>
+      <c r="H2" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="I2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
